--- a/data/OP2/case22_1/case22_operational_data.xlsx
+++ b/data/OP2/case22_1/case22_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case22_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case22_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38138985-53C4-AF42-B732-D24A07DBAD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3587B5A-6DBB-7D4F-A936-6331C46814DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="680" windowWidth="28440" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="680" windowWidth="28440" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -454,15 +454,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <f>E2*2</f>
-        <v>3.356E-2</v>
+        <f>E2*1.6</f>
+        <v>2.6848E-2</v>
       </c>
       <c r="C2">
-        <v>2.0910000000000002E-2</v>
+        <f>F2*1.6</f>
+        <v>3.3456000000000007E-2</v>
       </c>
       <c r="D2" s="2">
         <f>B2/SUM(B$2:B$33)</f>
-        <v>2.5335529683185087E-2</v>
+        <v>2.5335529683185091E-2</v>
       </c>
       <c r="E2">
         <v>1.678E-2</v>
@@ -476,15 +477,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B22" si="0">E3*2</f>
-        <v>3.356E-2</v>
+        <f t="shared" ref="B3:B22" si="0">E3*1.6</f>
+        <v>2.6848E-2</v>
       </c>
       <c r="C3">
-        <v>2.0910000000000002E-2</v>
+        <f t="shared" ref="C3:C22" si="1">F3*1.6</f>
+        <v>3.3456000000000007E-2</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D22" si="1">B3/SUM(B$2:B$33)</f>
-        <v>2.5335529683185087E-2</v>
+        <f t="shared" ref="D3:D22" si="2">B3/SUM(B$2:B$33)</f>
+        <v>2.5335529683185091E-2</v>
       </c>
       <c r="E3">
         <v>1.678E-2</v>
@@ -499,14 +501,15 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>6.7599999999999993E-2</v>
+        <v>5.4079999999999996E-2</v>
       </c>
       <c r="C4">
-        <v>3.7319999999999999E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.9712000000000001E-2</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="1"/>
-        <v>5.1033426894615964E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.1033426894615971E-2</v>
       </c>
       <c r="E4">
         <v>3.3799999999999997E-2</v>
@@ -521,14 +524,15 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>2.912E-2</v>
+        <v>2.3296000000000001E-2</v>
       </c>
       <c r="C5">
-        <v>1.252E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.0032000000000001E-2</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="1"/>
-        <v>2.1983630046911493E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.1983630046911496E-2</v>
       </c>
       <c r="E5">
         <v>1.456E-2</v>
@@ -543,14 +547,15 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>2.0980000000000002E-2</v>
+        <v>1.6784000000000004E-2</v>
       </c>
       <c r="C6">
-        <v>1.421E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.2736000000000003E-2</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="1"/>
-        <v>1.583848071374324E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.5838480713743244E-2</v>
       </c>
       <c r="E6">
         <v>1.0490000000000001E-2</v>
@@ -565,14 +570,15 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>1.7641999999999998E-2</v>
+        <v>1.4113599999999999E-2</v>
       </c>
       <c r="C7">
-        <v>1.166E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.8656000000000002E-2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="1"/>
-        <v>1.3318516527733946E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.3318516527733948E-2</v>
       </c>
       <c r="E7">
         <v>8.820999999999999E-3</v>
@@ -587,14 +593,15 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>2.87E-2</v>
+        <v>2.2960000000000001E-2</v>
       </c>
       <c r="C8">
-        <v>1.8589999999999999E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.9744E-2</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="1"/>
-        <v>2.1666558459696422E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.1666558459696426E-2</v>
       </c>
       <c r="E8">
         <v>1.435E-2</v>
@@ -609,14 +616,15 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>3.8619999999999995E-2</v>
+        <v>3.0895999999999996E-2</v>
       </c>
       <c r="C9">
-        <v>2.5870000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.1392000000000005E-2</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="1"/>
-        <v>2.915548737677616E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.9155487376776163E-2</v>
       </c>
       <c r="E9">
         <v>1.9309999999999997E-2</v>
@@ -631,14 +639,15 @@
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>2.87E-2</v>
+        <v>2.2960000000000001E-2</v>
       </c>
       <c r="C10">
-        <v>1.8589999999999999E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.9744E-2</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="1"/>
-        <v>2.1666558459696422E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.1666558459696426E-2</v>
       </c>
       <c r="E10">
         <v>1.435E-2</v>
@@ -653,14 +662,15 @@
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>3.2539999999999999E-2</v>
+        <v>2.6032E-2</v>
       </c>
       <c r="C11">
-        <v>1.9480000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.1168000000000001E-2</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="1"/>
-        <v>2.4565498685662775E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4565498685662778E-2</v>
       </c>
       <c r="E11">
         <v>1.627E-2</v>
@@ -675,14 +685,15 @@
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>3.2539999999999999E-2</v>
+        <v>2.6032E-2</v>
       </c>
       <c r="C12">
-        <v>1.9480000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.1168000000000001E-2</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="1"/>
-        <v>2.4565498685662775E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.4565498685662778E-2</v>
       </c>
       <c r="E12">
         <v>1.627E-2</v>
@@ -697,14 +708,15 @@
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>0.16425999999999999</v>
+        <v>0.131408</v>
       </c>
       <c r="C13">
-        <v>7.1650000000000005E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.11464000000000002</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="1"/>
-        <v>0.1240051878951127</v>
+        <f t="shared" si="2"/>
+        <v>0.12400518789511271</v>
       </c>
       <c r="E13">
         <v>8.2129999999999995E-2</v>
@@ -719,14 +731,15 @@
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>6.9419999999999996E-2</v>
+        <v>5.5536000000000002E-2</v>
       </c>
       <c r="C14">
-        <v>3.0120000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.8192000000000006E-2</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="1"/>
-        <v>5.2407403772547934E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.2407403772547941E-2</v>
       </c>
       <c r="E14">
         <v>3.4709999999999998E-2</v>
@@ -741,14 +754,15 @@
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>6.9419999999999996E-2</v>
+        <v>5.5536000000000002E-2</v>
       </c>
       <c r="C15">
-        <v>3.0120000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.8192000000000006E-2</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="1"/>
-        <v>5.2407403772547934E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.2407403772547941E-2</v>
       </c>
       <c r="E15">
         <v>3.4709999999999998E-2</v>
@@ -763,14 +777,15 @@
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
-        <v>0.16062000000000001</v>
+        <v>0.12849600000000003</v>
       </c>
       <c r="C16">
-        <v>7.0120000000000002E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.11219200000000001</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="1"/>
-        <v>0.12125723413924877</v>
+        <f t="shared" si="2"/>
+        <v>0.1212572341392488</v>
       </c>
       <c r="E16">
         <v>8.0310000000000006E-2</v>
@@ -785,14 +800,15 @@
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
-        <v>9.9239999999999995E-2</v>
+        <v>7.9392000000000004E-2</v>
       </c>
       <c r="C17">
-        <v>4.7820000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.6512000000000011E-2</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="1"/>
-        <v>7.4919486464817872E-2</v>
+        <f t="shared" si="2"/>
+        <v>7.4919486464817886E-2</v>
       </c>
       <c r="E17">
         <v>4.9619999999999997E-2</v>
@@ -807,14 +823,15 @@
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
-        <v>9.9239999999999995E-2</v>
+        <v>7.9392000000000004E-2</v>
       </c>
       <c r="C18">
-        <v>4.7820000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.6512000000000011E-2</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="1"/>
-        <v>7.4919486464817872E-2</v>
+        <f t="shared" si="2"/>
+        <v>7.4919486464817886E-2</v>
       </c>
       <c r="E18">
         <v>4.9619999999999997E-2</v>
@@ -829,14 +846,15 @@
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
-        <v>8.7540000000000007E-2</v>
+        <v>7.0032000000000011E-2</v>
       </c>
       <c r="C19">
-        <v>3.8929999999999999E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.2288000000000003E-2</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="1"/>
-        <v>6.6086777963826657E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.6086777963826671E-2</v>
       </c>
       <c r="E19">
         <v>4.3770000000000003E-2</v>
@@ -851,14 +869,15 @@
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
-        <v>7.4639999999999998E-2</v>
+        <v>5.9712000000000001E-2</v>
       </c>
       <c r="C20">
-        <v>3.5959999999999999E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.7536000000000004E-2</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="1"/>
-        <v>5.6348150642220943E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.634815064222095E-2</v>
       </c>
       <c r="E20">
         <v>3.7319999999999999E-2</v>
@@ -873,14 +892,15 @@
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
-        <v>7.4639999999999998E-2</v>
+        <v>5.9712000000000001E-2</v>
       </c>
       <c r="C21">
-        <v>3.5959999999999999E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.7536000000000004E-2</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="1"/>
-        <v>5.6348150642220943E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.634815064222095E-2</v>
       </c>
       <c r="E21">
         <v>3.7319999999999999E-2</v>
@@ -895,14 +915,15 @@
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
-        <v>6.2039999999999998E-2</v>
+        <v>4.9632000000000003E-2</v>
       </c>
       <c r="C22">
-        <v>2.9360000000000001E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.6976000000000004E-2</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" si="1"/>
-        <v>4.6836003025768853E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.683600302576886E-2</v>
       </c>
       <c r="E22">
         <v>3.1019999999999999E-2</v>
